--- a/engineer_forms/010_equipment_vibration_test_report_form--engineer_forms.xlsx
+++ b/engineer_forms/010_equipment_vibration_test_report_form--engineer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1810,109 +1810,109 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>test_frequency_resolution_choices</t>
+          <t>test_environment_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>test_frequency_resolution_choices</t>
+          <t>test_environment_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>test_frequency_resolution_choices</t>
+          <t>test_duration_range_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>test_frequency_resolution_choices</t>
+          <t>test_duration_range_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>test_frequency_resolution_choices</t>
+          <t>test_level_range_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>test_frequency_resolution_choices</t>
+          <t>test_level_range_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>test_environment_choices</t>
+          <t>test_frequency_range_2_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1929,7 +1929,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>test_environment_choices</t>
+          <t>test_frequency_range_2_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1946,7 +1946,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>test_duration_range_choices</t>
+          <t>test_frequency_range_3_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1963,7 +1963,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>test_duration_range_choices</t>
+          <t>test_frequency_range_3_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1980,134 +1980,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>test_level_range_choices</t>
+          <t>test_frequency_range_4_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>test_level_range_choices</t>
+          <t>test_frequency_range_4_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>test_frequency_range_2_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>test_frequency_range_2_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>test_frequency_range_3_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>test_frequency_range_3_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>test_frequency_range_4_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>test_frequency_range_4_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
         <is>
           <t>No</t>
         </is>
